--- a/LedgerPath_Money_Tracker.xlsx
+++ b/LedgerPath_Money_Tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\MicroS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/04e9bb415d956f31/Desktop/solfound/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E646805D-825B-4717-8246-CB1B7C2DB7EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{E646805D-825B-4717-8246-CB1B7C2DB7EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F730975-FF48-4292-A1FD-00732E80E294}"/>
   <bookViews>
-    <workbookView xWindow="-8130" yWindow="-16365" windowWidth="29040" windowHeight="15720" tabRatio="860" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17070" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="126">
   <si>
     <t>💰  MICRO-BUSINESS MONEY TRACKER — Dashboard</t>
   </si>
@@ -416,10 +416,7 @@
     <t>Bundle / Subscription</t>
   </si>
   <si>
-    <t>Basil</t>
-  </si>
-  <si>
-    <t>Dill</t>
+    <t>Raw Materials</t>
   </si>
 </sst>
 </file>
@@ -852,20 +849,11 @@
     <xf numFmtId="0" fontId="18" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -881,6 +869,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -951,6 +948,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1250,7 +1251,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="66"/>
@@ -1260,7 +1261,7 @@
       <c r="F1" s="66"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="67" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="66"/>
@@ -1270,14 +1271,14 @@
       <c r="F2" s="66"/>
     </row>
     <row r="3" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="70" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="66"/>
       <c r="C3" s="1">
         <v>2026</v>
       </c>
-      <c r="D3" s="71" t="s">
+      <c r="D3" s="68" t="s">
         <v>3</v>
       </c>
       <c r="E3" s="66"/>
@@ -1414,11 +1415,11 @@
       </c>
       <c r="C10" s="5">
         <f>IFERROR(SUMIF('Expense Log'!C:C,5,'Expense Log'!E:E),0)</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D10" s="6">
         <f t="shared" si="0"/>
-        <v>85.903999999999996</v>
+        <v>-4.0960000000000036</v>
       </c>
       <c r="E10" s="7">
         <f t="shared" si="1"/>
@@ -1426,7 +1427,7 @@
       </c>
       <c r="F10" s="6">
         <f t="shared" si="2"/>
-        <v>73.0184</v>
+        <v>-16.9816</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1615,11 +1616,11 @@
       </c>
       <c r="C19" s="15">
         <f>SUM(C6:C17)</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D19" s="6">
         <f>SUM(D6:D17)</f>
-        <v>85.903999999999996</v>
+        <v>-4.0960000000000036</v>
       </c>
       <c r="E19" s="16">
         <f>SUM(E6:E17)</f>
@@ -1627,12 +1628,12 @@
       </c>
       <c r="F19" s="6">
         <f>SUM(F6:F17)</f>
-        <v>73.0184</v>
+        <v>-16.9816</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="22" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="72" t="s">
+      <c r="A22" s="69" t="s">
         <v>23</v>
       </c>
       <c r="B22" s="66"/>
@@ -1696,11 +1697,11 @@
       </c>
       <c r="C25" s="10">
         <f>SUM(C9:C11)</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D25" s="11">
         <f>B25-C25</f>
-        <v>85.903999999999996</v>
+        <v>-4.0960000000000036</v>
       </c>
       <c r="E25" s="12">
         <f>B25*0.15</f>
@@ -1708,7 +1709,7 @@
       </c>
       <c r="F25" s="11">
         <f>D25-E25</f>
-        <v>73.0184</v>
+        <v>-16.9816</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1807,7 +1808,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="71" t="s">
         <v>29</v>
       </c>
       <c r="B1" s="66"/>
@@ -1818,7 +1819,7 @@
       <c r="G1" s="66"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="67" t="s">
         <v>30</v>
       </c>
       <c r="B2" s="66"/>
@@ -1869,9 +1870,7 @@
         <f>6.06*2*4.2</f>
         <v>50.903999999999996</v>
       </c>
-      <c r="F4" s="29" t="s">
-        <v>125</v>
-      </c>
+      <c r="F4" s="29"/>
       <c r="G4" s="30" t="str">
         <f t="shared" ref="G4:G35" si="1">IF(D4="","",IF(D4="Other Income","Verify deductibility","Taxable income — report on Schedule C"))</f>
         <v>Taxable income — report on Schedule C</v>
@@ -1894,9 +1893,7 @@
       <c r="E5" s="28">
         <v>35</v>
       </c>
-      <c r="F5" s="33" t="s">
-        <v>126</v>
-      </c>
+      <c r="F5" s="33"/>
       <c r="G5" s="34" t="str">
         <f t="shared" si="1"/>
         <v>Taxable income — report on Schedule C</v>
@@ -5301,7 +5298,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="72" t="s">
         <v>38</v>
       </c>
       <c r="B1" s="66"/>
@@ -5313,7 +5310,7 @@
       <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="67" t="s">
         <v>39</v>
       </c>
       <c r="B2" s="66"/>
@@ -5354,24 +5351,26 @@
       <c r="A4" s="36">
         <v>1</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="37" t="str">
-        <f t="shared" ref="C4:C35" si="0">IF(B4="","",MONTH(B4))</f>
-        <v/>
+      <c r="B4" s="25">
+        <v>46143</v>
+      </c>
+      <c r="C4" s="37">
+        <f t="shared" ref="C4:C7" si="0">IF(B4="","",MONTH(B4))</f>
+        <v>5</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="E4" s="28">
         <v>10</v>
       </c>
       <c r="F4" s="38" t="str">
         <f t="shared" ref="F4:F35" si="1">IF(D4="","",IF(D4="Seeds &amp; Soil","Yes",IF(D4="Tools &amp; Equipment","Yes",IF(D4="Bags &amp; Packaging","Yes",IF(D4="Water/Electricity","Partial",IF(D4="Transportation / Gas","Yes",IF(D4="Marketing","Yes",IF(D4="Insurance","Yes",IF(D4="Permits / Filing","Yes",IF(D4="Phone / Internet","Partial","Verify"))))))))))</f>
-        <v>Yes</v>
+        <v>Verify</v>
       </c>
       <c r="G4" s="39"/>
       <c r="H4" s="40" t="str">
-        <f t="shared" ref="H4:H35" si="2">IF(D4="","",IF(D4="Seeds &amp; Soil","Schedule C supplies",IF(D4="Tools &amp; Equipment","Depreciate or Section 179",IF(D4="Bags &amp; Packaging","Schedule C supplies",IF(D4="Water/Electricity","Business portion only — estimate %",IF(D4="Transportation / Gas","Track miles at IRS rate (67¢/mi 2024)",IF(D4="Marketing","Fully deductible",IF(D4="Insurance","Business insurance — fully deductible",IF(D4="Permits / Filing","Business licenses",IF(D4="Phone / Internet","Business use % only","Ask your tax pro"))))))))))</f>
+        <f>IF(D4="","",IF(D4="Raw Materials","Schedule C supplies",IF(D4="Tools &amp; Equipment","Depreciate or Section 179",IF(D4="Bags &amp; Packaging","Schedule C supplies",IF(D4="Water/Electricity","Business portion only — estimate %",IF(D4="Transportation / Gas","Track miles at IRS rate (67¢/mi 2024)",IF(D4="Marketing","Fully deductible",IF(D4="Insurance","Business insurance — fully deductible",IF(D4="Permits / Filing","Business licenses",IF(D4="Phone / Internet","Business use % only","Ask your tax pro"))))))))))</f>
         <v>Schedule C supplies</v>
       </c>
     </row>
@@ -5379,63 +5378,81 @@
       <c r="A5" s="31">
         <v>2</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="32" t="str">
+      <c r="B5" s="25">
+        <v>46145</v>
+      </c>
+      <c r="C5" s="32">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D5" s="27"/>
-      <c r="E5" s="28"/>
+        <v>5</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" s="28">
+        <v>20</v>
+      </c>
       <c r="F5" s="41" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="G5" s="33"/>
       <c r="H5" s="34" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <f t="shared" ref="H5:H35" si="2">IF(D5="","",IF(D5="Seeds &amp; Soil","Schedule C supplies",IF(D5="Tools &amp; Equipment","Depreciate or Section 179",IF(D5="Bags &amp; Packaging","Schedule C supplies",IF(D5="Water/Electricity","Business portion only — estimate %",IF(D5="Transportation / Gas","Track miles at IRS rate (67¢/mi 2024)",IF(D5="Marketing","Fully deductible",IF(D5="Insurance","Business insurance — fully deductible",IF(D5="Permits / Filing","Business licenses",IF(D5="Phone / Internet","Business use % only","Ask your tax pro"))))))))))</f>
+        <v>Schedule C supplies</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="36">
         <v>3</v>
       </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="37" t="str">
+      <c r="B6" s="25">
+        <v>46146</v>
+      </c>
+      <c r="C6" s="37">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D6" s="27"/>
-      <c r="E6" s="28"/>
+        <v>5</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" s="28">
+        <v>50</v>
+      </c>
       <c r="F6" s="38" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="G6" s="39"/>
       <c r="H6" s="40" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Depreciate or Section 179</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="31">
         <v>4</v>
       </c>
-      <c r="B7" s="25"/>
-      <c r="C7" s="32" t="str">
+      <c r="B7" s="25">
+        <v>46146</v>
+      </c>
+      <c r="C7" s="32">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D7" s="27"/>
-      <c r="E7" s="28"/>
+        <v>5</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" s="28">
+        <v>10</v>
+      </c>
       <c r="F7" s="41" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Partial</v>
       </c>
       <c r="G7" s="33"/>
       <c r="H7" s="34" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>Business portion only — estimate %</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5444,7 +5461,7 @@
       </c>
       <c r="B8" s="25"/>
       <c r="C8" s="37" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="C4:C35" si="3">IF(B8="","",MONTH(B8))</f>
         <v/>
       </c>
       <c r="D8" s="27"/>
@@ -5465,7 +5482,7 @@
       </c>
       <c r="B9" s="25"/>
       <c r="C9" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="D9" s="27"/>
@@ -5486,7 +5503,7 @@
       </c>
       <c r="B10" s="25"/>
       <c r="C10" s="37" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="D10" s="27"/>
@@ -5507,7 +5524,7 @@
       </c>
       <c r="B11" s="25"/>
       <c r="C11" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="D11" s="27"/>
@@ -5528,7 +5545,7 @@
       </c>
       <c r="B12" s="25"/>
       <c r="C12" s="37" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="D12" s="27"/>
@@ -5549,7 +5566,7 @@
       </c>
       <c r="B13" s="25"/>
       <c r="C13" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="D13" s="27"/>
@@ -5570,7 +5587,7 @@
       </c>
       <c r="B14" s="25"/>
       <c r="C14" s="37" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="D14" s="27"/>
@@ -5591,7 +5608,7 @@
       </c>
       <c r="B15" s="25"/>
       <c r="C15" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="D15" s="27"/>
@@ -5612,7 +5629,7 @@
       </c>
       <c r="B16" s="25"/>
       <c r="C16" s="37" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="D16" s="27"/>
@@ -5633,7 +5650,7 @@
       </c>
       <c r="B17" s="25"/>
       <c r="C17" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="D17" s="27"/>
@@ -5654,7 +5671,7 @@
       </c>
       <c r="B18" s="25"/>
       <c r="C18" s="37" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="D18" s="27"/>
@@ -5675,7 +5692,7 @@
       </c>
       <c r="B19" s="25"/>
       <c r="C19" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="D19" s="27"/>
@@ -5696,7 +5713,7 @@
       </c>
       <c r="B20" s="25"/>
       <c r="C20" s="37" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="D20" s="27"/>
@@ -5717,7 +5734,7 @@
       </c>
       <c r="B21" s="25"/>
       <c r="C21" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="D21" s="27"/>
@@ -5738,7 +5755,7 @@
       </c>
       <c r="B22" s="25"/>
       <c r="C22" s="37" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="D22" s="27"/>
@@ -5759,7 +5776,7 @@
       </c>
       <c r="B23" s="25"/>
       <c r="C23" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="D23" s="27"/>
@@ -5780,7 +5797,7 @@
       </c>
       <c r="B24" s="25"/>
       <c r="C24" s="37" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="D24" s="27"/>
@@ -5801,7 +5818,7 @@
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="D25" s="27"/>
@@ -5822,7 +5839,7 @@
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="37" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="D26" s="27"/>
@@ -5843,7 +5860,7 @@
       </c>
       <c r="B27" s="25"/>
       <c r="C27" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="D27" s="27"/>
@@ -5864,7 +5881,7 @@
       </c>
       <c r="B28" s="25"/>
       <c r="C28" s="37" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="D28" s="27"/>
@@ -5885,7 +5902,7 @@
       </c>
       <c r="B29" s="25"/>
       <c r="C29" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="D29" s="27"/>
@@ -5906,7 +5923,7 @@
       </c>
       <c r="B30" s="25"/>
       <c r="C30" s="37" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="D30" s="27"/>
@@ -5927,7 +5944,7 @@
       </c>
       <c r="B31" s="25"/>
       <c r="C31" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="D31" s="27"/>
@@ -5948,7 +5965,7 @@
       </c>
       <c r="B32" s="25"/>
       <c r="C32" s="37" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="D32" s="27"/>
@@ -5969,7 +5986,7 @@
       </c>
       <c r="B33" s="25"/>
       <c r="C33" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="D33" s="27"/>
@@ -5990,7 +6007,7 @@
       </c>
       <c r="B34" s="25"/>
       <c r="C34" s="37" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="D34" s="27"/>
@@ -6011,7 +6028,7 @@
       </c>
       <c r="B35" s="25"/>
       <c r="C35" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="D35" s="27"/>
@@ -6032,18 +6049,18 @@
       </c>
       <c r="B36" s="25"/>
       <c r="C36" s="37" t="str">
-        <f t="shared" ref="C36:C67" si="3">IF(B36="","",MONTH(B36))</f>
+        <f t="shared" ref="C36:C67" si="4">IF(B36="","",MONTH(B36))</f>
         <v/>
       </c>
       <c r="D36" s="27"/>
       <c r="E36" s="28"/>
       <c r="F36" s="38" t="str">
-        <f t="shared" ref="F36:F67" si="4">IF(D36="","",IF(D36="Seeds &amp; Soil","Yes",IF(D36="Tools &amp; Equipment","Yes",IF(D36="Bags &amp; Packaging","Yes",IF(D36="Water/Electricity","Partial",IF(D36="Transportation / Gas","Yes",IF(D36="Marketing","Yes",IF(D36="Insurance","Yes",IF(D36="Permits / Filing","Yes",IF(D36="Phone / Internet","Partial","Verify"))))))))))</f>
+        <f t="shared" ref="F36:F67" si="5">IF(D36="","",IF(D36="Seeds &amp; Soil","Yes",IF(D36="Tools &amp; Equipment","Yes",IF(D36="Bags &amp; Packaging","Yes",IF(D36="Water/Electricity","Partial",IF(D36="Transportation / Gas","Yes",IF(D36="Marketing","Yes",IF(D36="Insurance","Yes",IF(D36="Permits / Filing","Yes",IF(D36="Phone / Internet","Partial","Verify"))))))))))</f>
         <v/>
       </c>
       <c r="G36" s="39"/>
       <c r="H36" s="40" t="str">
-        <f t="shared" ref="H36:H67" si="5">IF(D36="","",IF(D36="Seeds &amp; Soil","Schedule C supplies",IF(D36="Tools &amp; Equipment","Depreciate or Section 179",IF(D36="Bags &amp; Packaging","Schedule C supplies",IF(D36="Water/Electricity","Business portion only — estimate %",IF(D36="Transportation / Gas","Track miles at IRS rate (67¢/mi 2024)",IF(D36="Marketing","Fully deductible",IF(D36="Insurance","Business insurance — fully deductible",IF(D36="Permits / Filing","Business licenses",IF(D36="Phone / Internet","Business use % only","Ask your tax pro"))))))))))</f>
+        <f t="shared" ref="H36:H67" si="6">IF(D36="","",IF(D36="Seeds &amp; Soil","Schedule C supplies",IF(D36="Tools &amp; Equipment","Depreciate or Section 179",IF(D36="Bags &amp; Packaging","Schedule C supplies",IF(D36="Water/Electricity","Business portion only — estimate %",IF(D36="Transportation / Gas","Track miles at IRS rate (67¢/mi 2024)",IF(D36="Marketing","Fully deductible",IF(D36="Insurance","Business insurance — fully deductible",IF(D36="Permits / Filing","Business licenses",IF(D36="Phone / Internet","Business use % only","Ask your tax pro"))))))))))</f>
         <v/>
       </c>
     </row>
@@ -6053,18 +6070,18 @@
       </c>
       <c r="B37" s="25"/>
       <c r="C37" s="32" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D37" s="27"/>
       <c r="E37" s="28"/>
       <c r="F37" s="41" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G37" s="33"/>
       <c r="H37" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6074,18 +6091,18 @@
       </c>
       <c r="B38" s="25"/>
       <c r="C38" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D38" s="27"/>
       <c r="E38" s="28"/>
       <c r="F38" s="38" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G38" s="39"/>
       <c r="H38" s="40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6095,18 +6112,18 @@
       </c>
       <c r="B39" s="25"/>
       <c r="C39" s="32" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D39" s="27"/>
       <c r="E39" s="28"/>
       <c r="F39" s="41" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G39" s="33"/>
       <c r="H39" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6116,18 +6133,18 @@
       </c>
       <c r="B40" s="25"/>
       <c r="C40" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D40" s="27"/>
       <c r="E40" s="28"/>
       <c r="F40" s="38" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G40" s="39"/>
       <c r="H40" s="40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6137,18 +6154,18 @@
       </c>
       <c r="B41" s="25"/>
       <c r="C41" s="32" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D41" s="27"/>
       <c r="E41" s="28"/>
       <c r="F41" s="41" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G41" s="33"/>
       <c r="H41" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6158,18 +6175,18 @@
       </c>
       <c r="B42" s="25"/>
       <c r="C42" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D42" s="27"/>
       <c r="E42" s="28"/>
       <c r="F42" s="38" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G42" s="39"/>
       <c r="H42" s="40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6179,18 +6196,18 @@
       </c>
       <c r="B43" s="25"/>
       <c r="C43" s="32" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="28"/>
       <c r="F43" s="41" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G43" s="33"/>
       <c r="H43" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6200,18 +6217,18 @@
       </c>
       <c r="B44" s="25"/>
       <c r="C44" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D44" s="27"/>
       <c r="E44" s="28"/>
       <c r="F44" s="38" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G44" s="39"/>
       <c r="H44" s="40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6221,18 +6238,18 @@
       </c>
       <c r="B45" s="25"/>
       <c r="C45" s="32" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D45" s="27"/>
       <c r="E45" s="28"/>
       <c r="F45" s="41" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G45" s="33"/>
       <c r="H45" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6242,18 +6259,18 @@
       </c>
       <c r="B46" s="25"/>
       <c r="C46" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D46" s="27"/>
       <c r="E46" s="28"/>
       <c r="F46" s="38" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G46" s="39"/>
       <c r="H46" s="40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6263,18 +6280,18 @@
       </c>
       <c r="B47" s="25"/>
       <c r="C47" s="32" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D47" s="27"/>
       <c r="E47" s="28"/>
       <c r="F47" s="41" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G47" s="33"/>
       <c r="H47" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6284,18 +6301,18 @@
       </c>
       <c r="B48" s="25"/>
       <c r="C48" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D48" s="27"/>
       <c r="E48" s="28"/>
       <c r="F48" s="38" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G48" s="39"/>
       <c r="H48" s="40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6305,18 +6322,18 @@
       </c>
       <c r="B49" s="25"/>
       <c r="C49" s="32" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D49" s="27"/>
       <c r="E49" s="28"/>
       <c r="F49" s="41" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G49" s="33"/>
       <c r="H49" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6326,18 +6343,18 @@
       </c>
       <c r="B50" s="25"/>
       <c r="C50" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D50" s="27"/>
       <c r="E50" s="28"/>
       <c r="F50" s="38" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G50" s="39"/>
       <c r="H50" s="40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6347,18 +6364,18 @@
       </c>
       <c r="B51" s="25"/>
       <c r="C51" s="32" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D51" s="27"/>
       <c r="E51" s="28"/>
       <c r="F51" s="41" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G51" s="33"/>
       <c r="H51" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6368,18 +6385,18 @@
       </c>
       <c r="B52" s="25"/>
       <c r="C52" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D52" s="27"/>
       <c r="E52" s="28"/>
       <c r="F52" s="38" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G52" s="39"/>
       <c r="H52" s="40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6389,18 +6406,18 @@
       </c>
       <c r="B53" s="25"/>
       <c r="C53" s="32" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D53" s="27"/>
       <c r="E53" s="28"/>
       <c r="F53" s="41" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G53" s="33"/>
       <c r="H53" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6410,18 +6427,18 @@
       </c>
       <c r="B54" s="25"/>
       <c r="C54" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D54" s="27"/>
       <c r="E54" s="28"/>
       <c r="F54" s="38" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G54" s="39"/>
       <c r="H54" s="40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6431,18 +6448,18 @@
       </c>
       <c r="B55" s="25"/>
       <c r="C55" s="32" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D55" s="27"/>
       <c r="E55" s="28"/>
       <c r="F55" s="41" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G55" s="33"/>
       <c r="H55" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6452,18 +6469,18 @@
       </c>
       <c r="B56" s="25"/>
       <c r="C56" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D56" s="27"/>
       <c r="E56" s="28"/>
       <c r="F56" s="38" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G56" s="39"/>
       <c r="H56" s="40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6473,18 +6490,18 @@
       </c>
       <c r="B57" s="25"/>
       <c r="C57" s="32" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D57" s="27"/>
       <c r="E57" s="28"/>
       <c r="F57" s="41" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G57" s="33"/>
       <c r="H57" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6494,18 +6511,18 @@
       </c>
       <c r="B58" s="25"/>
       <c r="C58" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D58" s="27"/>
       <c r="E58" s="28"/>
       <c r="F58" s="38" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G58" s="39"/>
       <c r="H58" s="40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6515,18 +6532,18 @@
       </c>
       <c r="B59" s="25"/>
       <c r="C59" s="32" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D59" s="27"/>
       <c r="E59" s="28"/>
       <c r="F59" s="41" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G59" s="33"/>
       <c r="H59" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6536,18 +6553,18 @@
       </c>
       <c r="B60" s="25"/>
       <c r="C60" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D60" s="27"/>
       <c r="E60" s="28"/>
       <c r="F60" s="38" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G60" s="39"/>
       <c r="H60" s="40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6557,18 +6574,18 @@
       </c>
       <c r="B61" s="25"/>
       <c r="C61" s="32" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D61" s="27"/>
       <c r="E61" s="28"/>
       <c r="F61" s="41" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G61" s="33"/>
       <c r="H61" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6578,18 +6595,18 @@
       </c>
       <c r="B62" s="25"/>
       <c r="C62" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D62" s="27"/>
       <c r="E62" s="28"/>
       <c r="F62" s="38" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G62" s="39"/>
       <c r="H62" s="40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6599,18 +6616,18 @@
       </c>
       <c r="B63" s="25"/>
       <c r="C63" s="32" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D63" s="27"/>
       <c r="E63" s="28"/>
       <c r="F63" s="41" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G63" s="33"/>
       <c r="H63" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6620,18 +6637,18 @@
       </c>
       <c r="B64" s="25"/>
       <c r="C64" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D64" s="27"/>
       <c r="E64" s="28"/>
       <c r="F64" s="38" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G64" s="39"/>
       <c r="H64" s="40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6641,18 +6658,18 @@
       </c>
       <c r="B65" s="25"/>
       <c r="C65" s="32" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D65" s="27"/>
       <c r="E65" s="28"/>
       <c r="F65" s="41" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G65" s="33"/>
       <c r="H65" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6662,18 +6679,18 @@
       </c>
       <c r="B66" s="25"/>
       <c r="C66" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D66" s="27"/>
       <c r="E66" s="28"/>
       <c r="F66" s="38" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G66" s="39"/>
       <c r="H66" s="40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6683,18 +6700,18 @@
       </c>
       <c r="B67" s="25"/>
       <c r="C67" s="32" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D67" s="27"/>
       <c r="E67" s="28"/>
       <c r="F67" s="41" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="G67" s="33"/>
       <c r="H67" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6704,18 +6721,18 @@
       </c>
       <c r="B68" s="25"/>
       <c r="C68" s="37" t="str">
-        <f t="shared" ref="C68:C99" si="6">IF(B68="","",MONTH(B68))</f>
+        <f t="shared" ref="C68:C99" si="7">IF(B68="","",MONTH(B68))</f>
         <v/>
       </c>
       <c r="D68" s="27"/>
       <c r="E68" s="28"/>
       <c r="F68" s="38" t="str">
-        <f t="shared" ref="F68:F99" si="7">IF(D68="","",IF(D68="Seeds &amp; Soil","Yes",IF(D68="Tools &amp; Equipment","Yes",IF(D68="Bags &amp; Packaging","Yes",IF(D68="Water/Electricity","Partial",IF(D68="Transportation / Gas","Yes",IF(D68="Marketing","Yes",IF(D68="Insurance","Yes",IF(D68="Permits / Filing","Yes",IF(D68="Phone / Internet","Partial","Verify"))))))))))</f>
+        <f t="shared" ref="F68:F99" si="8">IF(D68="","",IF(D68="Seeds &amp; Soil","Yes",IF(D68="Tools &amp; Equipment","Yes",IF(D68="Bags &amp; Packaging","Yes",IF(D68="Water/Electricity","Partial",IF(D68="Transportation / Gas","Yes",IF(D68="Marketing","Yes",IF(D68="Insurance","Yes",IF(D68="Permits / Filing","Yes",IF(D68="Phone / Internet","Partial","Verify"))))))))))</f>
         <v/>
       </c>
       <c r="G68" s="39"/>
       <c r="H68" s="40" t="str">
-        <f t="shared" ref="H68:H99" si="8">IF(D68="","",IF(D68="Seeds &amp; Soil","Schedule C supplies",IF(D68="Tools &amp; Equipment","Depreciate or Section 179",IF(D68="Bags &amp; Packaging","Schedule C supplies",IF(D68="Water/Electricity","Business portion only — estimate %",IF(D68="Transportation / Gas","Track miles at IRS rate (67¢/mi 2024)",IF(D68="Marketing","Fully deductible",IF(D68="Insurance","Business insurance — fully deductible",IF(D68="Permits / Filing","Business licenses",IF(D68="Phone / Internet","Business use % only","Ask your tax pro"))))))))))</f>
+        <f t="shared" ref="H68:H99" si="9">IF(D68="","",IF(D68="Seeds &amp; Soil","Schedule C supplies",IF(D68="Tools &amp; Equipment","Depreciate or Section 179",IF(D68="Bags &amp; Packaging","Schedule C supplies",IF(D68="Water/Electricity","Business portion only — estimate %",IF(D68="Transportation / Gas","Track miles at IRS rate (67¢/mi 2024)",IF(D68="Marketing","Fully deductible",IF(D68="Insurance","Business insurance — fully deductible",IF(D68="Permits / Filing","Business licenses",IF(D68="Phone / Internet","Business use % only","Ask your tax pro"))))))))))</f>
         <v/>
       </c>
     </row>
@@ -6725,18 +6742,18 @@
       </c>
       <c r="B69" s="25"/>
       <c r="C69" s="32" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D69" s="27"/>
       <c r="E69" s="28"/>
       <c r="F69" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G69" s="33"/>
       <c r="H69" s="34" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6746,18 +6763,18 @@
       </c>
       <c r="B70" s="25"/>
       <c r="C70" s="37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D70" s="27"/>
       <c r="E70" s="28"/>
       <c r="F70" s="38" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G70" s="39"/>
       <c r="H70" s="40" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6767,18 +6784,18 @@
       </c>
       <c r="B71" s="25"/>
       <c r="C71" s="32" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D71" s="27"/>
       <c r="E71" s="28"/>
       <c r="F71" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G71" s="33"/>
       <c r="H71" s="34" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6788,18 +6805,18 @@
       </c>
       <c r="B72" s="25"/>
       <c r="C72" s="37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D72" s="27"/>
       <c r="E72" s="28"/>
       <c r="F72" s="38" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G72" s="39"/>
       <c r="H72" s="40" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6809,18 +6826,18 @@
       </c>
       <c r="B73" s="25"/>
       <c r="C73" s="32" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D73" s="27"/>
       <c r="E73" s="28"/>
       <c r="F73" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G73" s="33"/>
       <c r="H73" s="34" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6830,18 +6847,18 @@
       </c>
       <c r="B74" s="25"/>
       <c r="C74" s="37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D74" s="27"/>
       <c r="E74" s="28"/>
       <c r="F74" s="38" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G74" s="39"/>
       <c r="H74" s="40" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6851,18 +6868,18 @@
       </c>
       <c r="B75" s="25"/>
       <c r="C75" s="32" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D75" s="27"/>
       <c r="E75" s="28"/>
       <c r="F75" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G75" s="33"/>
       <c r="H75" s="34" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6872,18 +6889,18 @@
       </c>
       <c r="B76" s="25"/>
       <c r="C76" s="37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D76" s="27"/>
       <c r="E76" s="28"/>
       <c r="F76" s="38" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G76" s="39"/>
       <c r="H76" s="40" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6893,18 +6910,18 @@
       </c>
       <c r="B77" s="25"/>
       <c r="C77" s="32" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D77" s="27"/>
       <c r="E77" s="28"/>
       <c r="F77" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G77" s="33"/>
       <c r="H77" s="34" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6914,18 +6931,18 @@
       </c>
       <c r="B78" s="25"/>
       <c r="C78" s="37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="28"/>
       <c r="F78" s="38" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G78" s="39"/>
       <c r="H78" s="40" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6935,18 +6952,18 @@
       </c>
       <c r="B79" s="25"/>
       <c r="C79" s="32" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D79" s="27"/>
       <c r="E79" s="28"/>
       <c r="F79" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G79" s="33"/>
       <c r="H79" s="34" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6956,18 +6973,18 @@
       </c>
       <c r="B80" s="25"/>
       <c r="C80" s="37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="28"/>
       <c r="F80" s="38" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G80" s="39"/>
       <c r="H80" s="40" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6977,18 +6994,18 @@
       </c>
       <c r="B81" s="25"/>
       <c r="C81" s="32" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="28"/>
       <c r="F81" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G81" s="33"/>
       <c r="H81" s="34" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6998,18 +7015,18 @@
       </c>
       <c r="B82" s="25"/>
       <c r="C82" s="37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="28"/>
       <c r="F82" s="38" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G82" s="39"/>
       <c r="H82" s="40" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7019,18 +7036,18 @@
       </c>
       <c r="B83" s="25"/>
       <c r="C83" s="32" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D83" s="27"/>
       <c r="E83" s="28"/>
       <c r="F83" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G83" s="33"/>
       <c r="H83" s="34" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7040,18 +7057,18 @@
       </c>
       <c r="B84" s="25"/>
       <c r="C84" s="37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="28"/>
       <c r="F84" s="38" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G84" s="39"/>
       <c r="H84" s="40" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7061,18 +7078,18 @@
       </c>
       <c r="B85" s="25"/>
       <c r="C85" s="32" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D85" s="27"/>
       <c r="E85" s="28"/>
       <c r="F85" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G85" s="33"/>
       <c r="H85" s="34" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7082,18 +7099,18 @@
       </c>
       <c r="B86" s="25"/>
       <c r="C86" s="37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D86" s="27"/>
       <c r="E86" s="28"/>
       <c r="F86" s="38" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G86" s="39"/>
       <c r="H86" s="40" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7103,18 +7120,18 @@
       </c>
       <c r="B87" s="25"/>
       <c r="C87" s="32" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D87" s="27"/>
       <c r="E87" s="28"/>
       <c r="F87" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G87" s="33"/>
       <c r="H87" s="34" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7124,18 +7141,18 @@
       </c>
       <c r="B88" s="25"/>
       <c r="C88" s="37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D88" s="27"/>
       <c r="E88" s="28"/>
       <c r="F88" s="38" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G88" s="39"/>
       <c r="H88" s="40" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7145,18 +7162,18 @@
       </c>
       <c r="B89" s="25"/>
       <c r="C89" s="32" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D89" s="27"/>
       <c r="E89" s="28"/>
       <c r="F89" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G89" s="33"/>
       <c r="H89" s="34" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7166,18 +7183,18 @@
       </c>
       <c r="B90" s="25"/>
       <c r="C90" s="37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D90" s="27"/>
       <c r="E90" s="28"/>
       <c r="F90" s="38" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G90" s="39"/>
       <c r="H90" s="40" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7187,18 +7204,18 @@
       </c>
       <c r="B91" s="25"/>
       <c r="C91" s="32" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D91" s="27"/>
       <c r="E91" s="28"/>
       <c r="F91" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G91" s="33"/>
       <c r="H91" s="34" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7208,18 +7225,18 @@
       </c>
       <c r="B92" s="25"/>
       <c r="C92" s="37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D92" s="27"/>
       <c r="E92" s="28"/>
       <c r="F92" s="38" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G92" s="39"/>
       <c r="H92" s="40" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7229,18 +7246,18 @@
       </c>
       <c r="B93" s="25"/>
       <c r="C93" s="32" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D93" s="27"/>
       <c r="E93" s="28"/>
       <c r="F93" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G93" s="33"/>
       <c r="H93" s="34" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7250,18 +7267,18 @@
       </c>
       <c r="B94" s="25"/>
       <c r="C94" s="37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D94" s="27"/>
       <c r="E94" s="28"/>
       <c r="F94" s="38" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G94" s="39"/>
       <c r="H94" s="40" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7271,18 +7288,18 @@
       </c>
       <c r="B95" s="25"/>
       <c r="C95" s="32" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D95" s="27"/>
       <c r="E95" s="28"/>
       <c r="F95" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G95" s="33"/>
       <c r="H95" s="34" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7292,18 +7309,18 @@
       </c>
       <c r="B96" s="25"/>
       <c r="C96" s="37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D96" s="27"/>
       <c r="E96" s="28"/>
       <c r="F96" s="38" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G96" s="39"/>
       <c r="H96" s="40" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7313,18 +7330,18 @@
       </c>
       <c r="B97" s="25"/>
       <c r="C97" s="32" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="28"/>
       <c r="F97" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G97" s="33"/>
       <c r="H97" s="34" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7334,18 +7351,18 @@
       </c>
       <c r="B98" s="25"/>
       <c r="C98" s="37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D98" s="27"/>
       <c r="E98" s="28"/>
       <c r="F98" s="38" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G98" s="39"/>
       <c r="H98" s="40" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7355,18 +7372,18 @@
       </c>
       <c r="B99" s="25"/>
       <c r="C99" s="32" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="D99" s="27"/>
       <c r="E99" s="28"/>
       <c r="F99" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="G99" s="33"/>
       <c r="H99" s="34" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7376,18 +7393,18 @@
       </c>
       <c r="B100" s="25"/>
       <c r="C100" s="37" t="str">
-        <f t="shared" ref="C100:C131" si="9">IF(B100="","",MONTH(B100))</f>
+        <f t="shared" ref="C100:C131" si="10">IF(B100="","",MONTH(B100))</f>
         <v/>
       </c>
       <c r="D100" s="27"/>
       <c r="E100" s="28"/>
       <c r="F100" s="38" t="str">
-        <f t="shared" ref="F100:F131" si="10">IF(D100="","",IF(D100="Seeds &amp; Soil","Yes",IF(D100="Tools &amp; Equipment","Yes",IF(D100="Bags &amp; Packaging","Yes",IF(D100="Water/Electricity","Partial",IF(D100="Transportation / Gas","Yes",IF(D100="Marketing","Yes",IF(D100="Insurance","Yes",IF(D100="Permits / Filing","Yes",IF(D100="Phone / Internet","Partial","Verify"))))))))))</f>
+        <f t="shared" ref="F100:F131" si="11">IF(D100="","",IF(D100="Seeds &amp; Soil","Yes",IF(D100="Tools &amp; Equipment","Yes",IF(D100="Bags &amp; Packaging","Yes",IF(D100="Water/Electricity","Partial",IF(D100="Transportation / Gas","Yes",IF(D100="Marketing","Yes",IF(D100="Insurance","Yes",IF(D100="Permits / Filing","Yes",IF(D100="Phone / Internet","Partial","Verify"))))))))))</f>
         <v/>
       </c>
       <c r="G100" s="39"/>
       <c r="H100" s="40" t="str">
-        <f t="shared" ref="H100:H131" si="11">IF(D100="","",IF(D100="Seeds &amp; Soil","Schedule C supplies",IF(D100="Tools &amp; Equipment","Depreciate or Section 179",IF(D100="Bags &amp; Packaging","Schedule C supplies",IF(D100="Water/Electricity","Business portion only — estimate %",IF(D100="Transportation / Gas","Track miles at IRS rate (67¢/mi 2024)",IF(D100="Marketing","Fully deductible",IF(D100="Insurance","Business insurance — fully deductible",IF(D100="Permits / Filing","Business licenses",IF(D100="Phone / Internet","Business use % only","Ask your tax pro"))))))))))</f>
+        <f t="shared" ref="H100:H131" si="12">IF(D100="","",IF(D100="Seeds &amp; Soil","Schedule C supplies",IF(D100="Tools &amp; Equipment","Depreciate or Section 179",IF(D100="Bags &amp; Packaging","Schedule C supplies",IF(D100="Water/Electricity","Business portion only — estimate %",IF(D100="Transportation / Gas","Track miles at IRS rate (67¢/mi 2024)",IF(D100="Marketing","Fully deductible",IF(D100="Insurance","Business insurance — fully deductible",IF(D100="Permits / Filing","Business licenses",IF(D100="Phone / Internet","Business use % only","Ask your tax pro"))))))))))</f>
         <v/>
       </c>
     </row>
@@ -7397,18 +7414,18 @@
       </c>
       <c r="B101" s="25"/>
       <c r="C101" s="32" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D101" s="27"/>
       <c r="E101" s="28"/>
       <c r="F101" s="41" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G101" s="33"/>
       <c r="H101" s="34" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -7418,18 +7435,18 @@
       </c>
       <c r="B102" s="25"/>
       <c r="C102" s="37" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D102" s="27"/>
       <c r="E102" s="28"/>
       <c r="F102" s="38" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G102" s="39"/>
       <c r="H102" s="40" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -7439,18 +7456,18 @@
       </c>
       <c r="B103" s="25"/>
       <c r="C103" s="32" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D103" s="27"/>
       <c r="E103" s="28"/>
       <c r="F103" s="41" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G103" s="33"/>
       <c r="H103" s="34" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -7460,18 +7477,18 @@
       </c>
       <c r="B104" s="25"/>
       <c r="C104" s="37" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D104" s="27"/>
       <c r="E104" s="28"/>
       <c r="F104" s="38" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G104" s="39"/>
       <c r="H104" s="40" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -7481,18 +7498,18 @@
       </c>
       <c r="B105" s="25"/>
       <c r="C105" s="32" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D105" s="27"/>
       <c r="E105" s="28"/>
       <c r="F105" s="41" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G105" s="33"/>
       <c r="H105" s="34" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -7502,18 +7519,18 @@
       </c>
       <c r="B106" s="25"/>
       <c r="C106" s="37" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D106" s="27"/>
       <c r="E106" s="28"/>
       <c r="F106" s="38" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G106" s="39"/>
       <c r="H106" s="40" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -7523,18 +7540,18 @@
       </c>
       <c r="B107" s="25"/>
       <c r="C107" s="32" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D107" s="27"/>
       <c r="E107" s="28"/>
       <c r="F107" s="41" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G107" s="33"/>
       <c r="H107" s="34" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -7544,18 +7561,18 @@
       </c>
       <c r="B108" s="25"/>
       <c r="C108" s="37" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D108" s="27"/>
       <c r="E108" s="28"/>
       <c r="F108" s="38" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G108" s="39"/>
       <c r="H108" s="40" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -7565,18 +7582,18 @@
       </c>
       <c r="B109" s="25"/>
       <c r="C109" s="32" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D109" s="27"/>
       <c r="E109" s="28"/>
       <c r="F109" s="41" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G109" s="33"/>
       <c r="H109" s="34" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -7586,18 +7603,18 @@
       </c>
       <c r="B110" s="25"/>
       <c r="C110" s="37" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D110" s="27"/>
       <c r="E110" s="28"/>
       <c r="F110" s="38" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G110" s="39"/>
       <c r="H110" s="40" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -7607,18 +7624,18 @@
       </c>
       <c r="B111" s="25"/>
       <c r="C111" s="32" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D111" s="27"/>
       <c r="E111" s="28"/>
       <c r="F111" s="41" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G111" s="33"/>
       <c r="H111" s="34" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -7628,18 +7645,18 @@
       </c>
       <c r="B112" s="25"/>
       <c r="C112" s="37" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D112" s="27"/>
       <c r="E112" s="28"/>
       <c r="F112" s="38" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G112" s="39"/>
       <c r="H112" s="40" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -7649,18 +7666,18 @@
       </c>
       <c r="B113" s="25"/>
       <c r="C113" s="32" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D113" s="27"/>
       <c r="E113" s="28"/>
       <c r="F113" s="41" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G113" s="33"/>
       <c r="H113" s="34" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -7670,18 +7687,18 @@
       </c>
       <c r="B114" s="25"/>
       <c r="C114" s="37" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D114" s="27"/>
       <c r="E114" s="28"/>
       <c r="F114" s="38" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G114" s="39"/>
       <c r="H114" s="40" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -7691,18 +7708,18 @@
       </c>
       <c r="B115" s="25"/>
       <c r="C115" s="32" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D115" s="27"/>
       <c r="E115" s="28"/>
       <c r="F115" s="41" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G115" s="33"/>
       <c r="H115" s="34" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -7712,18 +7729,18 @@
       </c>
       <c r="B116" s="25"/>
       <c r="C116" s="37" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D116" s="27"/>
       <c r="E116" s="28"/>
       <c r="F116" s="38" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G116" s="39"/>
       <c r="H116" s="40" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -7733,18 +7750,18 @@
       </c>
       <c r="B117" s="25"/>
       <c r="C117" s="32" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D117" s="27"/>
       <c r="E117" s="28"/>
       <c r="F117" s="41" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G117" s="33"/>
       <c r="H117" s="34" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -7754,18 +7771,18 @@
       </c>
       <c r="B118" s="25"/>
       <c r="C118" s="37" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D118" s="27"/>
       <c r="E118" s="28"/>
       <c r="F118" s="38" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G118" s="39"/>
       <c r="H118" s="40" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -7775,18 +7792,18 @@
       </c>
       <c r="B119" s="25"/>
       <c r="C119" s="32" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D119" s="27"/>
       <c r="E119" s="28"/>
       <c r="F119" s="41" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G119" s="33"/>
       <c r="H119" s="34" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -7796,18 +7813,18 @@
       </c>
       <c r="B120" s="25"/>
       <c r="C120" s="37" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D120" s="27"/>
       <c r="E120" s="28"/>
       <c r="F120" s="38" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G120" s="39"/>
       <c r="H120" s="40" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -7817,18 +7834,18 @@
       </c>
       <c r="B121" s="25"/>
       <c r="C121" s="32" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D121" s="27"/>
       <c r="E121" s="28"/>
       <c r="F121" s="41" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G121" s="33"/>
       <c r="H121" s="34" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -7838,18 +7855,18 @@
       </c>
       <c r="B122" s="25"/>
       <c r="C122" s="37" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D122" s="27"/>
       <c r="E122" s="28"/>
       <c r="F122" s="38" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G122" s="39"/>
       <c r="H122" s="40" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -7859,18 +7876,18 @@
       </c>
       <c r="B123" s="25"/>
       <c r="C123" s="32" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D123" s="27"/>
       <c r="E123" s="28"/>
       <c r="F123" s="41" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G123" s="33"/>
       <c r="H123" s="34" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -7880,18 +7897,18 @@
       </c>
       <c r="B124" s="25"/>
       <c r="C124" s="37" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="28"/>
       <c r="F124" s="38" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G124" s="39"/>
       <c r="H124" s="40" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -7901,18 +7918,18 @@
       </c>
       <c r="B125" s="25"/>
       <c r="C125" s="32" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="28"/>
       <c r="F125" s="41" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G125" s="33"/>
       <c r="H125" s="34" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -7922,18 +7939,18 @@
       </c>
       <c r="B126" s="25"/>
       <c r="C126" s="37" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="28"/>
       <c r="F126" s="38" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G126" s="39"/>
       <c r="H126" s="40" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -7943,18 +7960,18 @@
       </c>
       <c r="B127" s="25"/>
       <c r="C127" s="32" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D127" s="27"/>
       <c r="E127" s="28"/>
       <c r="F127" s="41" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G127" s="33"/>
       <c r="H127" s="34" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -7964,18 +7981,18 @@
       </c>
       <c r="B128" s="25"/>
       <c r="C128" s="37" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D128" s="27"/>
       <c r="E128" s="28"/>
       <c r="F128" s="38" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G128" s="39"/>
       <c r="H128" s="40" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -7985,18 +8002,18 @@
       </c>
       <c r="B129" s="25"/>
       <c r="C129" s="32" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D129" s="27"/>
       <c r="E129" s="28"/>
       <c r="F129" s="41" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G129" s="33"/>
       <c r="H129" s="34" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -8006,18 +8023,18 @@
       </c>
       <c r="B130" s="25"/>
       <c r="C130" s="37" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D130" s="27"/>
       <c r="E130" s="28"/>
       <c r="F130" s="38" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G130" s="39"/>
       <c r="H130" s="40" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -8027,18 +8044,18 @@
       </c>
       <c r="B131" s="25"/>
       <c r="C131" s="32" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="D131" s="27"/>
       <c r="E131" s="28"/>
       <c r="F131" s="41" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="G131" s="33"/>
       <c r="H131" s="34" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -8048,18 +8065,18 @@
       </c>
       <c r="B132" s="25"/>
       <c r="C132" s="37" t="str">
-        <f t="shared" ref="C132:C163" si="12">IF(B132="","",MONTH(B132))</f>
+        <f t="shared" ref="C132:C163" si="13">IF(B132="","",MONTH(B132))</f>
         <v/>
       </c>
       <c r="D132" s="27"/>
       <c r="E132" s="28"/>
       <c r="F132" s="38" t="str">
-        <f t="shared" ref="F132:F163" si="13">IF(D132="","",IF(D132="Seeds &amp; Soil","Yes",IF(D132="Tools &amp; Equipment","Yes",IF(D132="Bags &amp; Packaging","Yes",IF(D132="Water/Electricity","Partial",IF(D132="Transportation / Gas","Yes",IF(D132="Marketing","Yes",IF(D132="Insurance","Yes",IF(D132="Permits / Filing","Yes",IF(D132="Phone / Internet","Partial","Verify"))))))))))</f>
+        <f t="shared" ref="F132:F163" si="14">IF(D132="","",IF(D132="Seeds &amp; Soil","Yes",IF(D132="Tools &amp; Equipment","Yes",IF(D132="Bags &amp; Packaging","Yes",IF(D132="Water/Electricity","Partial",IF(D132="Transportation / Gas","Yes",IF(D132="Marketing","Yes",IF(D132="Insurance","Yes",IF(D132="Permits / Filing","Yes",IF(D132="Phone / Internet","Partial","Verify"))))))))))</f>
         <v/>
       </c>
       <c r="G132" s="39"/>
       <c r="H132" s="40" t="str">
-        <f t="shared" ref="H132:H163" si="14">IF(D132="","",IF(D132="Seeds &amp; Soil","Schedule C supplies",IF(D132="Tools &amp; Equipment","Depreciate or Section 179",IF(D132="Bags &amp; Packaging","Schedule C supplies",IF(D132="Water/Electricity","Business portion only — estimate %",IF(D132="Transportation / Gas","Track miles at IRS rate (67¢/mi 2024)",IF(D132="Marketing","Fully deductible",IF(D132="Insurance","Business insurance — fully deductible",IF(D132="Permits / Filing","Business licenses",IF(D132="Phone / Internet","Business use % only","Ask your tax pro"))))))))))</f>
+        <f t="shared" ref="H132:H163" si="15">IF(D132="","",IF(D132="Seeds &amp; Soil","Schedule C supplies",IF(D132="Tools &amp; Equipment","Depreciate or Section 179",IF(D132="Bags &amp; Packaging","Schedule C supplies",IF(D132="Water/Electricity","Business portion only — estimate %",IF(D132="Transportation / Gas","Track miles at IRS rate (67¢/mi 2024)",IF(D132="Marketing","Fully deductible",IF(D132="Insurance","Business insurance — fully deductible",IF(D132="Permits / Filing","Business licenses",IF(D132="Phone / Internet","Business use % only","Ask your tax pro"))))))))))</f>
         <v/>
       </c>
     </row>
@@ -8069,18 +8086,18 @@
       </c>
       <c r="B133" s="25"/>
       <c r="C133" s="32" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D133" s="27"/>
       <c r="E133" s="28"/>
       <c r="F133" s="41" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G133" s="33"/>
       <c r="H133" s="34" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8090,18 +8107,18 @@
       </c>
       <c r="B134" s="25"/>
       <c r="C134" s="37" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D134" s="27"/>
       <c r="E134" s="28"/>
       <c r="F134" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G134" s="39"/>
       <c r="H134" s="40" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8111,18 +8128,18 @@
       </c>
       <c r="B135" s="25"/>
       <c r="C135" s="32" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D135" s="27"/>
       <c r="E135" s="28"/>
       <c r="F135" s="41" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G135" s="33"/>
       <c r="H135" s="34" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8132,18 +8149,18 @@
       </c>
       <c r="B136" s="25"/>
       <c r="C136" s="37" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D136" s="27"/>
       <c r="E136" s="28"/>
       <c r="F136" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G136" s="39"/>
       <c r="H136" s="40" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8153,18 +8170,18 @@
       </c>
       <c r="B137" s="25"/>
       <c r="C137" s="32" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D137" s="27"/>
       <c r="E137" s="28"/>
       <c r="F137" s="41" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G137" s="33"/>
       <c r="H137" s="34" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8174,18 +8191,18 @@
       </c>
       <c r="B138" s="25"/>
       <c r="C138" s="37" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D138" s="27"/>
       <c r="E138" s="28"/>
       <c r="F138" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G138" s="39"/>
       <c r="H138" s="40" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8195,18 +8212,18 @@
       </c>
       <c r="B139" s="25"/>
       <c r="C139" s="32" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D139" s="27"/>
       <c r="E139" s="28"/>
       <c r="F139" s="41" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G139" s="33"/>
       <c r="H139" s="34" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8216,18 +8233,18 @@
       </c>
       <c r="B140" s="25"/>
       <c r="C140" s="37" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D140" s="27"/>
       <c r="E140" s="28"/>
       <c r="F140" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G140" s="39"/>
       <c r="H140" s="40" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8237,18 +8254,18 @@
       </c>
       <c r="B141" s="25"/>
       <c r="C141" s="32" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D141" s="27"/>
       <c r="E141" s="28"/>
       <c r="F141" s="41" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G141" s="33"/>
       <c r="H141" s="34" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8258,18 +8275,18 @@
       </c>
       <c r="B142" s="25"/>
       <c r="C142" s="37" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D142" s="27"/>
       <c r="E142" s="28"/>
       <c r="F142" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G142" s="39"/>
       <c r="H142" s="40" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8279,18 +8296,18 @@
       </c>
       <c r="B143" s="25"/>
       <c r="C143" s="32" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D143" s="27"/>
       <c r="E143" s="28"/>
       <c r="F143" s="41" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G143" s="33"/>
       <c r="H143" s="34" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8300,18 +8317,18 @@
       </c>
       <c r="B144" s="25"/>
       <c r="C144" s="37" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D144" s="27"/>
       <c r="E144" s="28"/>
       <c r="F144" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G144" s="39"/>
       <c r="H144" s="40" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8321,18 +8338,18 @@
       </c>
       <c r="B145" s="25"/>
       <c r="C145" s="32" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D145" s="27"/>
       <c r="E145" s="28"/>
       <c r="F145" s="41" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G145" s="33"/>
       <c r="H145" s="34" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8342,18 +8359,18 @@
       </c>
       <c r="B146" s="25"/>
       <c r="C146" s="37" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D146" s="27"/>
       <c r="E146" s="28"/>
       <c r="F146" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G146" s="39"/>
       <c r="H146" s="40" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8363,18 +8380,18 @@
       </c>
       <c r="B147" s="25"/>
       <c r="C147" s="32" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D147" s="27"/>
       <c r="E147" s="28"/>
       <c r="F147" s="41" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G147" s="33"/>
       <c r="H147" s="34" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8384,18 +8401,18 @@
       </c>
       <c r="B148" s="25"/>
       <c r="C148" s="37" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D148" s="27"/>
       <c r="E148" s="28"/>
       <c r="F148" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G148" s="39"/>
       <c r="H148" s="40" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8405,18 +8422,18 @@
       </c>
       <c r="B149" s="25"/>
       <c r="C149" s="32" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D149" s="27"/>
       <c r="E149" s="28"/>
       <c r="F149" s="41" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G149" s="33"/>
       <c r="H149" s="34" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8426,18 +8443,18 @@
       </c>
       <c r="B150" s="25"/>
       <c r="C150" s="37" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D150" s="27"/>
       <c r="E150" s="28"/>
       <c r="F150" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G150" s="39"/>
       <c r="H150" s="40" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8447,18 +8464,18 @@
       </c>
       <c r="B151" s="25"/>
       <c r="C151" s="32" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D151" s="27"/>
       <c r="E151" s="28"/>
       <c r="F151" s="41" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G151" s="33"/>
       <c r="H151" s="34" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8468,18 +8485,18 @@
       </c>
       <c r="B152" s="25"/>
       <c r="C152" s="37" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D152" s="27"/>
       <c r="E152" s="28"/>
       <c r="F152" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G152" s="39"/>
       <c r="H152" s="40" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8489,18 +8506,18 @@
       </c>
       <c r="B153" s="25"/>
       <c r="C153" s="32" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D153" s="27"/>
       <c r="E153" s="28"/>
       <c r="F153" s="41" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G153" s="33"/>
       <c r="H153" s="34" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8510,18 +8527,18 @@
       </c>
       <c r="B154" s="25"/>
       <c r="C154" s="37" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D154" s="27"/>
       <c r="E154" s="28"/>
       <c r="F154" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G154" s="39"/>
       <c r="H154" s="40" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8531,18 +8548,18 @@
       </c>
       <c r="B155" s="25"/>
       <c r="C155" s="32" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D155" s="27"/>
       <c r="E155" s="28"/>
       <c r="F155" s="41" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G155" s="33"/>
       <c r="H155" s="34" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8552,18 +8569,18 @@
       </c>
       <c r="B156" s="25"/>
       <c r="C156" s="37" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D156" s="27"/>
       <c r="E156" s="28"/>
       <c r="F156" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G156" s="39"/>
       <c r="H156" s="40" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8573,18 +8590,18 @@
       </c>
       <c r="B157" s="25"/>
       <c r="C157" s="32" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D157" s="27"/>
       <c r="E157" s="28"/>
       <c r="F157" s="41" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G157" s="33"/>
       <c r="H157" s="34" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8594,18 +8611,18 @@
       </c>
       <c r="B158" s="25"/>
       <c r="C158" s="37" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D158" s="27"/>
       <c r="E158" s="28"/>
       <c r="F158" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G158" s="39"/>
       <c r="H158" s="40" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8615,18 +8632,18 @@
       </c>
       <c r="B159" s="25"/>
       <c r="C159" s="32" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D159" s="27"/>
       <c r="E159" s="28"/>
       <c r="F159" s="41" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G159" s="33"/>
       <c r="H159" s="34" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8636,18 +8653,18 @@
       </c>
       <c r="B160" s="25"/>
       <c r="C160" s="37" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D160" s="27"/>
       <c r="E160" s="28"/>
       <c r="F160" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G160" s="39"/>
       <c r="H160" s="40" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8657,18 +8674,18 @@
       </c>
       <c r="B161" s="25"/>
       <c r="C161" s="32" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D161" s="27"/>
       <c r="E161" s="28"/>
       <c r="F161" s="41" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G161" s="33"/>
       <c r="H161" s="34" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8678,18 +8695,18 @@
       </c>
       <c r="B162" s="25"/>
       <c r="C162" s="37" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D162" s="27"/>
       <c r="E162" s="28"/>
       <c r="F162" s="38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G162" s="39"/>
       <c r="H162" s="40" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8699,18 +8716,18 @@
       </c>
       <c r="B163" s="25"/>
       <c r="C163" s="32" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D163" s="27"/>
       <c r="E163" s="28"/>
       <c r="F163" s="41" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="G163" s="33"/>
       <c r="H163" s="34" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -8720,18 +8737,18 @@
       </c>
       <c r="B164" s="25"/>
       <c r="C164" s="37" t="str">
-        <f t="shared" ref="C164:C195" si="15">IF(B164="","",MONTH(B164))</f>
+        <f t="shared" ref="C164:C195" si="16">IF(B164="","",MONTH(B164))</f>
         <v/>
       </c>
       <c r="D164" s="27"/>
       <c r="E164" s="28"/>
       <c r="F164" s="38" t="str">
-        <f t="shared" ref="F164:F195" si="16">IF(D164="","",IF(D164="Seeds &amp; Soil","Yes",IF(D164="Tools &amp; Equipment","Yes",IF(D164="Bags &amp; Packaging","Yes",IF(D164="Water/Electricity","Partial",IF(D164="Transportation / Gas","Yes",IF(D164="Marketing","Yes",IF(D164="Insurance","Yes",IF(D164="Permits / Filing","Yes",IF(D164="Phone / Internet","Partial","Verify"))))))))))</f>
+        <f t="shared" ref="F164:F195" si="17">IF(D164="","",IF(D164="Seeds &amp; Soil","Yes",IF(D164="Tools &amp; Equipment","Yes",IF(D164="Bags &amp; Packaging","Yes",IF(D164="Water/Electricity","Partial",IF(D164="Transportation / Gas","Yes",IF(D164="Marketing","Yes",IF(D164="Insurance","Yes",IF(D164="Permits / Filing","Yes",IF(D164="Phone / Internet","Partial","Verify"))))))))))</f>
         <v/>
       </c>
       <c r="G164" s="39"/>
       <c r="H164" s="40" t="str">
-        <f t="shared" ref="H164:H195" si="17">IF(D164="","",IF(D164="Seeds &amp; Soil","Schedule C supplies",IF(D164="Tools &amp; Equipment","Depreciate or Section 179",IF(D164="Bags &amp; Packaging","Schedule C supplies",IF(D164="Water/Electricity","Business portion only — estimate %",IF(D164="Transportation / Gas","Track miles at IRS rate (67¢/mi 2024)",IF(D164="Marketing","Fully deductible",IF(D164="Insurance","Business insurance — fully deductible",IF(D164="Permits / Filing","Business licenses",IF(D164="Phone / Internet","Business use % only","Ask your tax pro"))))))))))</f>
+        <f t="shared" ref="H164:H195" si="18">IF(D164="","",IF(D164="Seeds &amp; Soil","Schedule C supplies",IF(D164="Tools &amp; Equipment","Depreciate or Section 179",IF(D164="Bags &amp; Packaging","Schedule C supplies",IF(D164="Water/Electricity","Business portion only — estimate %",IF(D164="Transportation / Gas","Track miles at IRS rate (67¢/mi 2024)",IF(D164="Marketing","Fully deductible",IF(D164="Insurance","Business insurance — fully deductible",IF(D164="Permits / Filing","Business licenses",IF(D164="Phone / Internet","Business use % only","Ask your tax pro"))))))))))</f>
         <v/>
       </c>
     </row>
@@ -8741,18 +8758,18 @@
       </c>
       <c r="B165" s="25"/>
       <c r="C165" s="32" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D165" s="27"/>
       <c r="E165" s="28"/>
       <c r="F165" s="41" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G165" s="33"/>
       <c r="H165" s="34" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -8762,18 +8779,18 @@
       </c>
       <c r="B166" s="25"/>
       <c r="C166" s="37" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D166" s="27"/>
       <c r="E166" s="28"/>
       <c r="F166" s="38" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G166" s="39"/>
       <c r="H166" s="40" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -8783,18 +8800,18 @@
       </c>
       <c r="B167" s="25"/>
       <c r="C167" s="32" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D167" s="27"/>
       <c r="E167" s="28"/>
       <c r="F167" s="41" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G167" s="33"/>
       <c r="H167" s="34" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -8804,18 +8821,18 @@
       </c>
       <c r="B168" s="25"/>
       <c r="C168" s="37" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D168" s="27"/>
       <c r="E168" s="28"/>
       <c r="F168" s="38" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G168" s="39"/>
       <c r="H168" s="40" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -8825,18 +8842,18 @@
       </c>
       <c r="B169" s="25"/>
       <c r="C169" s="32" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D169" s="27"/>
       <c r="E169" s="28"/>
       <c r="F169" s="41" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G169" s="33"/>
       <c r="H169" s="34" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -8846,18 +8863,18 @@
       </c>
       <c r="B170" s="25"/>
       <c r="C170" s="37" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D170" s="27"/>
       <c r="E170" s="28"/>
       <c r="F170" s="38" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G170" s="39"/>
       <c r="H170" s="40" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -8867,18 +8884,18 @@
       </c>
       <c r="B171" s="25"/>
       <c r="C171" s="32" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D171" s="27"/>
       <c r="E171" s="28"/>
       <c r="F171" s="41" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G171" s="33"/>
       <c r="H171" s="34" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -8888,18 +8905,18 @@
       </c>
       <c r="B172" s="25"/>
       <c r="C172" s="37" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D172" s="27"/>
       <c r="E172" s="28"/>
       <c r="F172" s="38" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G172" s="39"/>
       <c r="H172" s="40" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -8909,18 +8926,18 @@
       </c>
       <c r="B173" s="25"/>
       <c r="C173" s="32" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D173" s="27"/>
       <c r="E173" s="28"/>
       <c r="F173" s="41" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G173" s="33"/>
       <c r="H173" s="34" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -8930,18 +8947,18 @@
       </c>
       <c r="B174" s="25"/>
       <c r="C174" s="37" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D174" s="27"/>
       <c r="E174" s="28"/>
       <c r="F174" s="38" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G174" s="39"/>
       <c r="H174" s="40" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -8951,18 +8968,18 @@
       </c>
       <c r="B175" s="25"/>
       <c r="C175" s="32" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D175" s="27"/>
       <c r="E175" s="28"/>
       <c r="F175" s="41" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G175" s="33"/>
       <c r="H175" s="34" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -8972,18 +8989,18 @@
       </c>
       <c r="B176" s="25"/>
       <c r="C176" s="37" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D176" s="27"/>
       <c r="E176" s="28"/>
       <c r="F176" s="38" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G176" s="39"/>
       <c r="H176" s="40" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -8993,18 +9010,18 @@
       </c>
       <c r="B177" s="25"/>
       <c r="C177" s="32" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D177" s="27"/>
       <c r="E177" s="28"/>
       <c r="F177" s="41" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G177" s="33"/>
       <c r="H177" s="34" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9014,18 +9031,18 @@
       </c>
       <c r="B178" s="25"/>
       <c r="C178" s="37" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D178" s="27"/>
       <c r="E178" s="28"/>
       <c r="F178" s="38" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G178" s="39"/>
       <c r="H178" s="40" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9035,18 +9052,18 @@
       </c>
       <c r="B179" s="25"/>
       <c r="C179" s="32" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D179" s="27"/>
       <c r="E179" s="28"/>
       <c r="F179" s="41" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G179" s="33"/>
       <c r="H179" s="34" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9056,18 +9073,18 @@
       </c>
       <c r="B180" s="25"/>
       <c r="C180" s="37" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D180" s="27"/>
       <c r="E180" s="28"/>
       <c r="F180" s="38" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G180" s="39"/>
       <c r="H180" s="40" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9077,18 +9094,18 @@
       </c>
       <c r="B181" s="25"/>
       <c r="C181" s="32" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D181" s="27"/>
       <c r="E181" s="28"/>
       <c r="F181" s="41" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G181" s="33"/>
       <c r="H181" s="34" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9098,18 +9115,18 @@
       </c>
       <c r="B182" s="25"/>
       <c r="C182" s="37" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D182" s="27"/>
       <c r="E182" s="28"/>
       <c r="F182" s="38" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G182" s="39"/>
       <c r="H182" s="40" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9119,18 +9136,18 @@
       </c>
       <c r="B183" s="25"/>
       <c r="C183" s="32" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D183" s="27"/>
       <c r="E183" s="28"/>
       <c r="F183" s="41" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G183" s="33"/>
       <c r="H183" s="34" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9140,18 +9157,18 @@
       </c>
       <c r="B184" s="25"/>
       <c r="C184" s="37" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D184" s="27"/>
       <c r="E184" s="28"/>
       <c r="F184" s="38" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G184" s="39"/>
       <c r="H184" s="40" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9161,18 +9178,18 @@
       </c>
       <c r="B185" s="25"/>
       <c r="C185" s="32" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D185" s="27"/>
       <c r="E185" s="28"/>
       <c r="F185" s="41" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G185" s="33"/>
       <c r="H185" s="34" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9182,18 +9199,18 @@
       </c>
       <c r="B186" s="25"/>
       <c r="C186" s="37" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D186" s="27"/>
       <c r="E186" s="28"/>
       <c r="F186" s="38" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G186" s="39"/>
       <c r="H186" s="40" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9203,18 +9220,18 @@
       </c>
       <c r="B187" s="25"/>
       <c r="C187" s="32" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D187" s="27"/>
       <c r="E187" s="28"/>
       <c r="F187" s="41" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G187" s="33"/>
       <c r="H187" s="34" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9224,18 +9241,18 @@
       </c>
       <c r="B188" s="25"/>
       <c r="C188" s="37" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D188" s="27"/>
       <c r="E188" s="28"/>
       <c r="F188" s="38" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G188" s="39"/>
       <c r="H188" s="40" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9245,18 +9262,18 @@
       </c>
       <c r="B189" s="25"/>
       <c r="C189" s="32" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D189" s="27"/>
       <c r="E189" s="28"/>
       <c r="F189" s="41" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G189" s="33"/>
       <c r="H189" s="34" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9266,18 +9283,18 @@
       </c>
       <c r="B190" s="25"/>
       <c r="C190" s="37" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D190" s="27"/>
       <c r="E190" s="28"/>
       <c r="F190" s="38" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G190" s="39"/>
       <c r="H190" s="40" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9287,18 +9304,18 @@
       </c>
       <c r="B191" s="25"/>
       <c r="C191" s="32" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D191" s="27"/>
       <c r="E191" s="28"/>
       <c r="F191" s="41" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G191" s="33"/>
       <c r="H191" s="34" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9308,18 +9325,18 @@
       </c>
       <c r="B192" s="25"/>
       <c r="C192" s="37" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D192" s="27"/>
       <c r="E192" s="28"/>
       <c r="F192" s="38" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G192" s="39"/>
       <c r="H192" s="40" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9329,18 +9346,18 @@
       </c>
       <c r="B193" s="25"/>
       <c r="C193" s="32" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D193" s="27"/>
       <c r="E193" s="28"/>
       <c r="F193" s="41" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G193" s="33"/>
       <c r="H193" s="34" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9350,18 +9367,18 @@
       </c>
       <c r="B194" s="25"/>
       <c r="C194" s="37" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D194" s="27"/>
       <c r="E194" s="28"/>
       <c r="F194" s="38" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G194" s="39"/>
       <c r="H194" s="40" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9371,18 +9388,18 @@
       </c>
       <c r="B195" s="25"/>
       <c r="C195" s="32" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="D195" s="27"/>
       <c r="E195" s="28"/>
       <c r="F195" s="41" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G195" s="33"/>
       <c r="H195" s="34" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -9392,18 +9409,18 @@
       </c>
       <c r="B196" s="25"/>
       <c r="C196" s="37" t="str">
-        <f t="shared" ref="C196:C203" si="18">IF(B196="","",MONTH(B196))</f>
+        <f t="shared" ref="C196:C203" si="19">IF(B196="","",MONTH(B196))</f>
         <v/>
       </c>
       <c r="D196" s="27"/>
       <c r="E196" s="28"/>
       <c r="F196" s="38" t="str">
-        <f t="shared" ref="F196:F203" si="19">IF(D196="","",IF(D196="Seeds &amp; Soil","Yes",IF(D196="Tools &amp; Equipment","Yes",IF(D196="Bags &amp; Packaging","Yes",IF(D196="Water/Electricity","Partial",IF(D196="Transportation / Gas","Yes",IF(D196="Marketing","Yes",IF(D196="Insurance","Yes",IF(D196="Permits / Filing","Yes",IF(D196="Phone / Internet","Partial","Verify"))))))))))</f>
+        <f t="shared" ref="F196:F203" si="20">IF(D196="","",IF(D196="Seeds &amp; Soil","Yes",IF(D196="Tools &amp; Equipment","Yes",IF(D196="Bags &amp; Packaging","Yes",IF(D196="Water/Electricity","Partial",IF(D196="Transportation / Gas","Yes",IF(D196="Marketing","Yes",IF(D196="Insurance","Yes",IF(D196="Permits / Filing","Yes",IF(D196="Phone / Internet","Partial","Verify"))))))))))</f>
         <v/>
       </c>
       <c r="G196" s="39"/>
       <c r="H196" s="40" t="str">
-        <f t="shared" ref="H196:H203" si="20">IF(D196="","",IF(D196="Seeds &amp; Soil","Schedule C supplies",IF(D196="Tools &amp; Equipment","Depreciate or Section 179",IF(D196="Bags &amp; Packaging","Schedule C supplies",IF(D196="Water/Electricity","Business portion only — estimate %",IF(D196="Transportation / Gas","Track miles at IRS rate (67¢/mi 2024)",IF(D196="Marketing","Fully deductible",IF(D196="Insurance","Business insurance — fully deductible",IF(D196="Permits / Filing","Business licenses",IF(D196="Phone / Internet","Business use % only","Ask your tax pro"))))))))))</f>
+        <f t="shared" ref="H196:H203" si="21">IF(D196="","",IF(D196="Seeds &amp; Soil","Schedule C supplies",IF(D196="Tools &amp; Equipment","Depreciate or Section 179",IF(D196="Bags &amp; Packaging","Schedule C supplies",IF(D196="Water/Electricity","Business portion only — estimate %",IF(D196="Transportation / Gas","Track miles at IRS rate (67¢/mi 2024)",IF(D196="Marketing","Fully deductible",IF(D196="Insurance","Business insurance — fully deductible",IF(D196="Permits / Filing","Business licenses",IF(D196="Phone / Internet","Business use % only","Ask your tax pro"))))))))))</f>
         <v/>
       </c>
     </row>
@@ -9413,18 +9430,18 @@
       </c>
       <c r="B197" s="25"/>
       <c r="C197" s="32" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="D197" s="27"/>
       <c r="E197" s="28"/>
       <c r="F197" s="41" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="G197" s="33"/>
       <c r="H197" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -9434,18 +9451,18 @@
       </c>
       <c r="B198" s="25"/>
       <c r="C198" s="37" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="D198" s="27"/>
       <c r="E198" s="28"/>
       <c r="F198" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="G198" s="39"/>
       <c r="H198" s="40" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -9455,18 +9472,18 @@
       </c>
       <c r="B199" s="25"/>
       <c r="C199" s="32" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="D199" s="27"/>
       <c r="E199" s="28"/>
       <c r="F199" s="41" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="G199" s="33"/>
       <c r="H199" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -9476,18 +9493,18 @@
       </c>
       <c r="B200" s="25"/>
       <c r="C200" s="37" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="D200" s="27"/>
       <c r="E200" s="28"/>
       <c r="F200" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="G200" s="39"/>
       <c r="H200" s="40" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -9497,18 +9514,18 @@
       </c>
       <c r="B201" s="25"/>
       <c r="C201" s="32" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="D201" s="27"/>
       <c r="E201" s="28"/>
       <c r="F201" s="41" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="G201" s="33"/>
       <c r="H201" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -9518,18 +9535,18 @@
       </c>
       <c r="B202" s="25"/>
       <c r="C202" s="37" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="D202" s="27"/>
       <c r="E202" s="28"/>
       <c r="F202" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="G202" s="39"/>
       <c r="H202" s="40" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -9539,18 +9556,18 @@
       </c>
       <c r="B203" s="25"/>
       <c r="C203" s="32" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="D203" s="27"/>
       <c r="E203" s="28"/>
       <c r="F203" s="41" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="G203" s="33"/>
       <c r="H203" s="34" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -9570,9 +9587,12 @@
       <formula>F4="Verify"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="list" sqref="D4:D500" xr:uid="{00000000-0002-0000-0200-000000000000}">
+  <dataValidations disablePrompts="1" count="2">
+    <dataValidation type="list" sqref="D204:D500" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Seeds &amp; Soil,Tools &amp; Equipment,Bags &amp; Packaging,Water/Electricity,Transportation / Gas,Marketing,Insurance,Permits / Filing,Phone / Internet,Other Expense"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="D4:D203" xr:uid="{EA55D55E-041A-4FCD-8B65-DD6B3A000860}">
+      <formula1>"Raw Materials,Tools &amp; Equipment,Bags &amp; Packaging,Water/Electricity,Transportation / Gas,Marketing,Insurance,Permits / Filing,Phone / Internet,Other Expense"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9593,7 +9613,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="73" t="s">
         <v>43</v>
       </c>
       <c r="B1" s="66"/>
@@ -9601,7 +9621,7 @@
       <c r="D1" s="66"/>
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="67" t="s">
         <v>44</v>
       </c>
       <c r="B2" s="66"/>
@@ -9609,7 +9629,7 @@
       <c r="D2" s="66"/>
     </row>
     <row r="3" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="74" t="s">
         <v>45</v>
       </c>
       <c r="B3" s="66"/>
@@ -9649,11 +9669,11 @@
       </c>
       <c r="B6" s="43">
         <f>IFERROR(SUMIF('Expense Log'!F4:F203,"Yes",'Expense Log'!E4:E203),0)</f>
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="C6" s="44">
         <f>IFERROR(B6/B5,0)</f>
-        <v>0.11640901471409947</v>
+        <v>0.81486310299869624</v>
       </c>
       <c r="D6" s="34" t="s">
         <v>51</v>
@@ -9665,11 +9685,11 @@
       </c>
       <c r="B7" s="45">
         <f>IFERROR(SUMIF('Expense Log'!F4:F203,"Partial",'Expense Log'!E4:E203),0)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C7" s="42">
         <f>IFERROR(B7/B5,0)</f>
-        <v>0</v>
+        <v>0.11640901471409947</v>
       </c>
       <c r="D7" s="30" t="s">
         <v>53</v>
@@ -9681,11 +9701,11 @@
       </c>
       <c r="B8" s="11">
         <f>B5-B6</f>
-        <v>75.903999999999996</v>
+        <v>15.903999999999996</v>
       </c>
       <c r="C8" s="44">
         <f>IFERROR(B8/B5,0)</f>
-        <v>0.88359098528590052</v>
+        <v>0.18513689700130376</v>
       </c>
       <c r="D8" s="34" t="s">
         <v>55</v>
@@ -9697,11 +9717,11 @@
       </c>
       <c r="B9" s="5">
         <f>B8*0.153</f>
-        <v>11.613311999999999</v>
+        <v>2.4333119999999995</v>
       </c>
       <c r="C9" s="42">
         <f>IFERROR(B9/B5,0)</f>
-        <v>0.13518942074874277</v>
+        <v>2.8325945241199475E-2</v>
       </c>
       <c r="D9" s="30" t="s">
         <v>57</v>
@@ -9713,11 +9733,11 @@
       </c>
       <c r="B10" s="10">
         <f>B8*0.12</f>
-        <v>9.1084799999999984</v>
+        <v>1.9084799999999995</v>
       </c>
       <c r="C10" s="44">
         <f>IFERROR(B10/B5,0)</f>
-        <v>0.10603091823430805</v>
+        <v>2.2216427640156449E-2</v>
       </c>
       <c r="D10" s="34" t="s">
         <v>59</v>
@@ -9729,11 +9749,11 @@
       </c>
       <c r="B11" s="15">
         <f>B9+B10</f>
-        <v>20.721791999999997</v>
+        <v>4.341791999999999</v>
       </c>
       <c r="C11" s="42">
         <f>IFERROR(B11/B5,0)</f>
-        <v>0.24122033898305081</v>
+        <v>5.0542372881355921E-2</v>
       </c>
       <c r="D11" s="30" t="s">
         <v>61</v>
@@ -9745,11 +9765,11 @@
       </c>
       <c r="B12" s="46">
         <f>B8-B11</f>
-        <v>55.182208000000003</v>
+        <v>11.562207999999998</v>
       </c>
       <c r="C12" s="44">
         <f>IFERROR(B12/B5,0)</f>
-        <v>0.64237064630284979</v>
+        <v>0.13459452411994782</v>
       </c>
       <c r="D12" s="34" t="s">
         <v>63</v>
@@ -9757,7 +9777,7 @@
     </row>
     <row r="14" spans="1:4" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="15" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="68" t="s">
+      <c r="A15" s="75" t="s">
         <v>64</v>
       </c>
       <c r="B15" s="66"/>
@@ -9844,7 +9864,7 @@
     </row>
     <row r="22" spans="1:4" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="23" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="67" t="s">
+      <c r="A23" s="74" t="s">
         <v>71</v>
       </c>
       <c r="B23" s="66"/>
@@ -9871,7 +9891,7 @@
       </c>
       <c r="B25" s="45">
         <f>IFERROR(SUMIF('Expense Log'!D4:D203,"Seeds &amp; Soil",'Expense Log'!E4:E203),0)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C25" s="52" t="s">
         <v>77</v>
@@ -9886,7 +9906,7 @@
       </c>
       <c r="B26" s="43">
         <f>IFERROR(SUMIF('Expense Log'!D4:D203,"Tools &amp; Equipment",'Expense Log'!E4:E203),0)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C26" s="54" t="s">
         <v>77</v>
@@ -9901,7 +9921,7 @@
       </c>
       <c r="B27" s="45">
         <f>IFERROR(SUMIF('Expense Log'!D4:D203,"Bags &amp; Packaging",'Expense Log'!E4:E203),0)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C27" s="52" t="s">
         <v>77</v>
@@ -9916,7 +9936,7 @@
       </c>
       <c r="B28" s="43">
         <f>IFERROR(SUMIF('Expense Log'!D4:D203,"Water/Electricity",'Expense Log'!E4:E203),0)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C28" s="54" t="s">
         <v>77</v>
@@ -10056,7 +10076,7 @@
       <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="67" t="s">
         <v>96</v>
       </c>
       <c r="B2" s="66"/>
@@ -11315,7 +11335,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="65" t="s">
         <v>103</v>
       </c>
       <c r="B1" s="66"/>
